--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-labresult.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-labresult.xlsx
@@ -273,7 +273,7 @@
 【JP Core仕様】検体検査結果レポートのプロフィール</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -1053,7 +1053,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートが関係するヘルスケアイベントに関する情報</t>
+    <t>診断レポートが関係する診療イベントに関する情報</t>
   </si>
   <si>
     <t>【JP Core仕様】入院外来の区別や所在場所、担当診療科の情報に使用する。  
